--- a/helper/test.xlsx
+++ b/helper/test.xlsx
@@ -397,62 +397,179 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:P3"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1"/>
+    <col min="11" max="11" width="11.83203125" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" customWidth="1"/>
+    <col min="13" max="13" width="11.83203125" customWidth="1"/>
+    <col min="14" max="14" width="11.83203125" customWidth="1"/>
+    <col min="15" max="15" width="11.83203125" customWidth="1"/>
+    <col min="16" max="16" width="11.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>fName</v>
+        <v>ชื่อจริง</v>
       </c>
       <c r="B1" t="str">
-        <v>lName</v>
+        <v>นามสกุล</v>
       </c>
       <c r="C1" t="str">
-        <v>email</v>
+        <v>คาบที่ 1</v>
       </c>
       <c r="D1" t="str">
-        <v>tel</v>
+        <v>คาบที่ 2</v>
       </c>
       <c r="E1" t="str">
-        <v>cityzenId</v>
+        <v>คาบที่ 3</v>
+      </c>
+      <c r="F1" t="str">
+        <v>คาบที่ 4</v>
+      </c>
+      <c r="G1" t="str">
+        <v>คาบที่ 5</v>
+      </c>
+      <c r="H1" t="str">
+        <v>คาบที่ 6</v>
+      </c>
+      <c r="I1" t="str">
+        <v>คาบที่ 7</v>
+      </c>
+      <c r="J1" t="str">
+        <v>คาบที่ 8</v>
+      </c>
+      <c r="K1" t="str">
+        <v>คาบที่ 9</v>
+      </c>
+      <c r="L1" t="str">
+        <v>คาบที่ 10</v>
+      </c>
+      <c r="M1" t="str">
+        <v>คาบที่ 11</v>
+      </c>
+      <c r="N1" t="str">
+        <v>คาบที่ 12</v>
+      </c>
+      <c r="O1" t="str">
+        <v>คาบที่ 13</v>
+      </c>
+      <c r="P1" t="str">
+        <v>คาบที่ 14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ควย</v>
+        <v>Peerapon</v>
       </c>
       <c r="B2" t="str">
-        <v>กูดำ</v>
+        <v>Loasuangkoon</v>
       </c>
       <c r="C2" t="str">
-        <v>kuygudum@gmail.com</v>
-      </c>
-      <c r="D2">
-        <v>99999999</v>
-      </c>
-      <c r="E2">
-        <v>1479900578276</v>
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="D2" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="E2" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="F2" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="G2" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="H2" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="I2" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="J2" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="K2" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="L2" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="M2" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="N2" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="O2" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="P2" t="str">
+        <v>เข้าเรียน</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>พีรพล</v>
+        <v>Johnny</v>
       </c>
       <c r="B3" t="str">
-        <v>เล่าสุอังกูร</v>
+        <v>Silverhand</v>
       </c>
       <c r="C3" t="str">
-        <v>peeraphol.l@kkumail.com</v>
-      </c>
-      <c r="D3">
-        <v>855555555</v>
-      </c>
-      <c r="E3">
-        <v>1479900578214</v>
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="D3" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="E3" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="F3" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="G3" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="H3" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="I3" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="J3" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="K3" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="L3" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="M3" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="N3" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="O3" t="str">
+        <v>เข้าเรียน</v>
+      </c>
+      <c r="P3" t="str">
+        <v>เข้าเรียน</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P3"/>
   </ignoredErrors>
 </worksheet>
 </file>